--- a/docs/Vysledky.xlsx
+++ b/docs/Vysledky.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fisar\Desktop\Diplomka\pytorch-template-master\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF02A0E-C06A-4CA9-8883-CC9FAA35CF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75720C3-FF4C-4CCD-8C1F-BF811A268BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3030" windowWidth="29040" windowHeight="15720" xr2:uid="{486FEA26-F7B0-4A22-B604-55840BBDFE20}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{486FEA26-F7B0-4A22-B604-55840BBDFE20}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -359,7 +359,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="132">
   <si>
     <t>0302_102215</t>
   </si>
@@ -752,6 +752,9 @@
   </si>
   <si>
     <t> 0,999954</t>
+  </si>
+  <si>
+    <t>ms/vzorek</t>
   </si>
 </sst>
 </file>
@@ -877,7 +880,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -939,22 +942,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -962,7 +953,34 @@
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
     <cellStyle name="Procenta" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000%"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1069,30 +1087,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="164" formatCode="0.00000000%"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1141,27 +1135,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D1D29E56-8840-4853-B8EE-7EC5113406CD}" name="Tabulka1" displayName="Tabulka1" ref="B1:P43" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="B1:P43" xr:uid="{D1D29E56-8840-4853-B8EE-7EC5113406CD}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:P34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D1D29E56-8840-4853-B8EE-7EC5113406CD}" name="Tabulka1" displayName="Tabulka1" ref="B1:Q43" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="B1:Q43" xr:uid="{D1D29E56-8840-4853-B8EE-7EC5113406CD}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:Q34">
     <sortCondition ref="C1:C34"/>
   </sortState>
-  <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{007C10F0-80F5-45AC-8F06-8029EA1E146D}" name="Dataset" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{02A94C36-9A62-42A6-9B71-02AECCF738F7}" name="Run" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{B3B717A2-8C61-480B-80A6-AB688F48BD0C}" name="Config" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{40C0E203-9511-43EF-BB61-862AF7264690}" name="parametry trén." dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{F406715E-884E-46C9-A93E-69FB54DA2578}" name="parametry celkem" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{C3A8C5CC-AEEC-48C3-A5BB-421EFDC8A637}" name="epoch" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{BEE715A4-984A-4FB8-8945-196C148DD614}" name="val_acc" dataDxfId="8" dataCellStyle="Procenta"/>
-    <tableColumn id="3" xr3:uid="{CEAF40B8-EE1B-40D3-8745-582D1F2D9F28}" name="test_acc_old" dataDxfId="7" dataCellStyle="Procenta"/>
-    <tableColumn id="6" xr3:uid="{2881E0AE-6597-42D2-98DF-943A17CB55C8}" name="test_acc_new" dataDxfId="4" dataCellStyle="Procenta"/>
-    <tableColumn id="7" xr3:uid="{FFFD3AC8-5CE3-431F-8648-28164CE2D5B5}" name="precision_macro" dataDxfId="3" dataCellStyle="Procenta"/>
-    <tableColumn id="9" xr3:uid="{AFE3CF12-D795-4E58-AFD8-2341D60AC416}" name="recall_macro" dataDxfId="2" dataCellStyle="Procenta"/>
-    <tableColumn id="15" xr3:uid="{823E727C-3D02-4E5D-8059-33FB98039E15}" name="f1_macro" dataDxfId="0" dataCellStyle="Procenta"/>
-    <tableColumn id="14" xr3:uid="{0AEBD2D4-DA7A-4568-ABF2-CAED24D1A773}" name="inference_time_s" dataDxfId="1" dataCellStyle="Procenta"/>
-    <tableColumn id="13" xr3:uid="{5927E27C-B8DF-4ED2-B7DC-DB97D9F59A7E}" name="doba trén." dataDxfId="6" dataCellStyle="Procenta"/>
-    <tableColumn id="8" xr3:uid="{7262171A-7AFF-46EF-99EC-9CE7B51F7712}" name="Poznámka" dataDxfId="5"/>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{007C10F0-80F5-45AC-8F06-8029EA1E146D}" name="Dataset" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{02A94C36-9A62-42A6-9B71-02AECCF738F7}" name="Run" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{B3B717A2-8C61-480B-80A6-AB688F48BD0C}" name="Config" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{40C0E203-9511-43EF-BB61-862AF7264690}" name="parametry trén." dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{F406715E-884E-46C9-A93E-69FB54DA2578}" name="parametry celkem" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{C3A8C5CC-AEEC-48C3-A5BB-421EFDC8A637}" name="epoch" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{BEE715A4-984A-4FB8-8945-196C148DD614}" name="val_acc" dataDxfId="9" dataCellStyle="Procenta"/>
+    <tableColumn id="3" xr3:uid="{CEAF40B8-EE1B-40D3-8745-582D1F2D9F28}" name="test_acc_old" dataDxfId="8" dataCellStyle="Procenta"/>
+    <tableColumn id="6" xr3:uid="{2881E0AE-6597-42D2-98DF-943A17CB55C8}" name="test_acc_new" dataDxfId="7" dataCellStyle="Procenta"/>
+    <tableColumn id="7" xr3:uid="{FFFD3AC8-5CE3-431F-8648-28164CE2D5B5}" name="precision_macro" dataDxfId="6" dataCellStyle="Procenta"/>
+    <tableColumn id="9" xr3:uid="{AFE3CF12-D795-4E58-AFD8-2341D60AC416}" name="recall_macro" dataDxfId="5" dataCellStyle="Procenta"/>
+    <tableColumn id="15" xr3:uid="{823E727C-3D02-4E5D-8059-33FB98039E15}" name="f1_macro" dataDxfId="4" dataCellStyle="Procenta"/>
+    <tableColumn id="14" xr3:uid="{0AEBD2D4-DA7A-4568-ABF2-CAED24D1A773}" name="inference_time_s" dataDxfId="3" dataCellStyle="Procenta"/>
+    <tableColumn id="16" xr3:uid="{9C56FC14-97C6-41AB-8418-119476FF8352}" name="ms/vzorek" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{5927E27C-B8DF-4ED2-B7DC-DB97D9F59A7E}" name="doba trén." dataDxfId="1" dataCellStyle="Procenta"/>
+    <tableColumn id="8" xr3:uid="{7262171A-7AFF-46EF-99EC-9CE7B51F7712}" name="Poznámka" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1484,7 +1479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29C24D65-FA7A-4955-9008-6EBD57198998}">
-  <dimension ref="B1:P54"/>
+  <dimension ref="B1:Q54"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="12.90625" customWidth="1"/>
@@ -1495,13 +1490,14 @@
     <col min="10" max="10" width="17.08984375" customWidth="1"/>
     <col min="11" max="11" width="17.1796875" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="16.08984375" customWidth="1"/>
-    <col min="14" max="14" width="15" customWidth="1"/>
-    <col min="15" max="15" width="16.81640625" customWidth="1"/>
-    <col min="16" max="16" width="53.36328125" customWidth="1"/>
+    <col min="13" max="14" width="16.08984375" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
+    <col min="16" max="16" width="16.81640625" customWidth="1"/>
+    <col min="17" max="17" width="51.90625" customWidth="1"/>
+    <col min="18" max="18" width="56.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="29" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>83</v>
       </c>
@@ -1542,13 +1538,16 @@
         <v>124</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B2" s="1">
         <v>1</v>
       </c>
@@ -1588,14 +1587,17 @@
       <c r="N2" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P2" s="8">
         <v>8.3133564814814823E-3</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:16" s="2" customFormat="1" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:17" s="2" customFormat="1" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1">
         <v>1</v>
       </c>
@@ -1635,14 +1637,17 @@
       <c r="N3" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O3" s="8">
+      <c r="O3" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P3" s="8">
         <v>4.0914351851851855E-2</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B4" s="1">
         <v>1</v>
       </c>
@@ -1682,14 +1687,17 @@
       <c r="N4" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O4" s="8">
+      <c r="O4" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P4" s="8">
         <v>9.2013888888888892E-3</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="Q4" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -1729,12 +1737,15 @@
       <c r="N5" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O5" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P5" s="8">
         <v>8.564814814814815E-3</v>
       </c>
-      <c r="P5" s="4"/>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q5" s="4"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B6" s="1">
         <v>1</v>
       </c>
@@ -1774,12 +1785,15 @@
       <c r="N6" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P6" s="8">
         <v>7.0486111111111114E-3</v>
       </c>
-      <c r="P6" s="4"/>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q6" s="4"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B7" s="1">
         <v>1</v>
       </c>
@@ -1819,12 +1833,15 @@
       <c r="N7" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O7" s="8">
+      <c r="O7" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P7" s="8">
         <v>2.1087962962962965E-2</v>
       </c>
-      <c r="P7" s="4"/>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q7" s="4"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B8" s="1">
         <v>1</v>
       </c>
@@ -1864,12 +1881,15 @@
       <c r="N8" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O8" s="8">
+      <c r="O8" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P8" s="8">
         <v>2.585648148148148E-2</v>
       </c>
-      <c r="P8" s="4"/>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q8" s="4"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B9" s="1">
         <v>1</v>
       </c>
@@ -1909,12 +1929,15 @@
       <c r="N9" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P9" s="8">
         <v>2.0775462962962964E-2</v>
       </c>
-      <c r="P9" s="4"/>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q9" s="4"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B10" s="1">
         <v>1</v>
       </c>
@@ -1954,12 +1977,15 @@
       <c r="N10" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P10" s="8">
         <v>2.1134259259259259E-2</v>
       </c>
-      <c r="P10" s="4"/>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q10" s="4"/>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B11" s="1">
         <v>2</v>
       </c>
@@ -1999,12 +2025,15 @@
       <c r="N11" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O11" s="8">
+      <c r="O11" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P11" s="8">
         <v>3.2129629629629633E-2</v>
       </c>
-      <c r="P11" s="4"/>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q11" s="4"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B12" s="1">
         <v>2</v>
       </c>
@@ -2044,12 +2073,15 @@
       <c r="N12" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P12" s="8">
         <v>1.9490740740740739E-2</v>
       </c>
-      <c r="P12" s="4"/>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q12" s="4"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B13" s="1">
         <v>2</v>
       </c>
@@ -2089,12 +2121,15 @@
       <c r="N13" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O13" s="8">
+      <c r="O13" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P13" s="8">
         <v>1.7395833333333333E-2</v>
       </c>
-      <c r="P13" s="4"/>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q13" s="4"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B14" s="1">
         <v>2</v>
       </c>
@@ -2134,12 +2169,15 @@
       <c r="N14" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O14" s="8">
+      <c r="O14" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P14" s="8">
         <v>2.1967592592592594E-2</v>
       </c>
-      <c r="P14" s="4"/>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q14" s="4"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B15" s="1">
         <v>2</v>
       </c>
@@ -2179,12 +2217,15 @@
       <c r="N15" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O15" s="8">
+      <c r="O15" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P15" s="8">
         <v>3.0185185185185186E-2</v>
       </c>
-      <c r="P15" s="4"/>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q15" s="4"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B16" s="1">
         <v>2</v>
       </c>
@@ -2224,12 +2265,15 @@
       <c r="N16" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O16" s="8">
+      <c r="O16" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P16" s="8">
         <v>1.3726851851851851E-2</v>
       </c>
-      <c r="P16" s="4"/>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q16" s="4"/>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B17" s="1">
         <v>2</v>
       </c>
@@ -2269,12 +2313,15 @@
       <c r="N17" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O17" s="8">
+      <c r="O17" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P17" s="8">
         <v>3.4502314814814812E-2</v>
       </c>
-      <c r="P17" s="4"/>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q17" s="4"/>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B18" s="1">
         <v>2</v>
       </c>
@@ -2314,12 +2361,15 @@
       <c r="N18" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O18" s="8">
+      <c r="O18" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P18" s="8">
         <v>0.03</v>
       </c>
-      <c r="P18" s="4"/>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q18" s="4"/>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B19" s="1">
         <v>2</v>
       </c>
@@ -2359,12 +2409,15 @@
       <c r="N19" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O19" s="8">
+      <c r="O19" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P19" s="8">
         <v>4.7118055555555559E-2</v>
       </c>
-      <c r="P19" s="4"/>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q19" s="4"/>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B20" s="1">
         <v>3</v>
       </c>
@@ -2404,14 +2457,17 @@
       <c r="N20" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O20" s="8">
+      <c r="O20" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P20" s="8">
         <v>1.3784722222222223E-2</v>
       </c>
-      <c r="P20" s="4" t="s">
+      <c r="Q20" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B21" s="1">
         <v>3</v>
       </c>
@@ -2451,14 +2507,17 @@
       <c r="N21" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O21" s="8">
+      <c r="O21" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P21" s="8">
         <v>1.7592592592592594E-2</v>
       </c>
-      <c r="P21" s="4" t="s">
+      <c r="Q21" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B22" s="1">
         <v>3</v>
       </c>
@@ -2498,14 +2557,17 @@
       <c r="N22" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O22" s="8">
+      <c r="O22" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P22" s="8">
         <v>1.7986111111111112E-2</v>
       </c>
-      <c r="P22" s="4" t="s">
+      <c r="Q22" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B23" s="1">
         <v>3</v>
       </c>
@@ -2545,14 +2607,17 @@
       <c r="N23" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O23" s="8">
+      <c r="O23" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P23" s="8">
         <v>2.7893518518518519E-2</v>
       </c>
-      <c r="P23" s="4" t="s">
+      <c r="Q23" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B24" s="1">
         <v>3</v>
       </c>
@@ -2592,14 +2657,17 @@
       <c r="N24" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O24" s="8">
+      <c r="O24" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P24" s="8">
         <v>3.0289351851851852E-2</v>
       </c>
-      <c r="P24" s="4" t="s">
+      <c r="Q24" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B25" s="1">
         <v>3</v>
       </c>
@@ -2639,14 +2707,17 @@
       <c r="N25" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O25" s="8">
+      <c r="O25" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P25" s="8">
         <v>4.4525462962962961E-2</v>
       </c>
-      <c r="P25" s="4" t="s">
+      <c r="Q25" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B26" s="1">
         <v>3</v>
       </c>
@@ -2686,14 +2757,17 @@
       <c r="N26" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O26" s="8">
+      <c r="O26" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P26" s="8">
         <v>2.6608796296296297E-2</v>
       </c>
-      <c r="P26" s="4" t="s">
+      <c r="Q26" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B27" s="1">
         <v>3</v>
       </c>
@@ -2733,14 +2807,17 @@
       <c r="N27" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O27" s="8">
+      <c r="O27" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P27" s="8">
         <v>1.7372685185185185E-2</v>
       </c>
-      <c r="P27" s="4" t="s">
+      <c r="Q27" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B28" s="1">
         <v>3</v>
       </c>
@@ -2780,14 +2857,17 @@
       <c r="N28" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O28" s="8">
+      <c r="O28" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P28" s="8">
         <v>2.9594907407407407E-2</v>
       </c>
-      <c r="P28" s="4" t="s">
+      <c r="Q28" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B29" s="1">
         <v>3</v>
       </c>
@@ -2827,14 +2907,17 @@
       <c r="N29" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O29" s="8">
+      <c r="O29" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P29" s="8">
         <v>0.18793981481481481</v>
       </c>
-      <c r="P29" s="4" t="s">
+      <c r="Q29" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B30" s="1">
         <v>3</v>
       </c>
@@ -2874,14 +2957,17 @@
       <c r="N30" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O30" s="8">
+      <c r="O30" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P30" s="8">
         <v>2.8032407407407409E-2</v>
       </c>
-      <c r="P30" s="4" t="s">
+      <c r="Q30" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B31" s="1">
         <v>3</v>
       </c>
@@ -2921,14 +3007,17 @@
       <c r="N31" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="O31" s="8">
+      <c r="O31" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P31" s="8">
         <v>0.1013425925925926</v>
       </c>
-      <c r="P31" s="4" t="s">
+      <c r="Q31" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B32" s="1">
         <v>4</v>
       </c>
@@ -2956,24 +3045,27 @@
       <c r="J32" s="6">
         <v>0.99998579797621101</v>
       </c>
-      <c r="K32" s="24">
+      <c r="K32" s="22">
         <v>0.99997599999999998</v>
       </c>
-      <c r="L32" s="24">
+      <c r="L32" s="22">
         <v>0.99996799999999997</v>
       </c>
-      <c r="M32" s="24">
+      <c r="M32" s="22">
         <v>0.99997199999999997</v>
       </c>
-      <c r="N32" s="21">
+      <c r="N32" s="10">
         <v>3.7002000000000002</v>
       </c>
-      <c r="O32" s="8">
+      <c r="O32" s="10">
+        <v>2.63E-2</v>
+      </c>
+      <c r="P32" s="8">
         <v>2.3807870370370372E-2</v>
       </c>
-      <c r="P32" s="4"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q32" s="4"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B33" s="1">
         <v>4</v>
       </c>
@@ -3001,24 +3093,27 @@
       <c r="J33" s="6">
         <v>0.99997869696431696</v>
       </c>
-      <c r="K33" s="24">
+      <c r="K33" s="22">
         <v>0.99995400000000001</v>
       </c>
-      <c r="L33" s="24">
+      <c r="L33" s="22">
         <v>0.99988500000000002</v>
       </c>
-      <c r="M33" s="24">
+      <c r="M33" s="22">
         <v>0.999919</v>
       </c>
-      <c r="N33" s="25">
+      <c r="N33" s="1">
         <v>5.9097</v>
       </c>
-      <c r="O33" s="8">
+      <c r="O33" s="1">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="P33" s="8">
         <v>1.5902777777777776E-2</v>
       </c>
-      <c r="P33" s="4"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q33" s="4"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B34" s="1">
         <v>4</v>
       </c>
@@ -3046,24 +3141,27 @@
       <c r="J34" s="6">
         <v>0.99997869696431696</v>
       </c>
-      <c r="K34" s="24">
+      <c r="K34" s="22">
         <v>0.99995400000000001</v>
       </c>
-      <c r="L34" s="24">
+      <c r="L34" s="22">
         <v>0.99988500000000002</v>
       </c>
-      <c r="M34" s="24" t="s">
+      <c r="M34" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="N34" s="21">
+      <c r="N34" s="10">
         <v>5.5284000000000004</v>
       </c>
-      <c r="O34" s="8">
+      <c r="O34" s="10">
+        <v>3.9300000000000002E-2</v>
+      </c>
+      <c r="P34" s="8">
         <v>1.7604166666666667E-2</v>
       </c>
-      <c r="P34" s="4"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q34" s="4"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B35" s="1">
         <v>4</v>
       </c>
@@ -3091,24 +3189,27 @@
       <c r="J35" s="6">
         <v>0.99998579797621101</v>
       </c>
-      <c r="K35" s="24">
+      <c r="K35" s="22">
         <v>0.99997599999999998</v>
       </c>
-      <c r="L35" s="24">
+      <c r="L35" s="22">
         <v>0.99996799999999997</v>
       </c>
-      <c r="M35" s="24">
+      <c r="M35" s="22">
         <v>0.99997199999999997</v>
       </c>
-      <c r="N35" s="26">
+      <c r="N35" s="1">
         <v>7.2676999999999996</v>
       </c>
-      <c r="O35" s="8">
+      <c r="O35" s="1">
+        <v>5.16E-2</v>
+      </c>
+      <c r="P35" s="8">
         <v>3.8819444444444441E-2</v>
       </c>
-      <c r="P35" s="4"/>
-    </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q35" s="4"/>
+    </row>
+    <row r="36" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B36" s="1">
         <v>4</v>
       </c>
@@ -3136,24 +3237,27 @@
       <c r="J36" s="6">
         <v>0.99997869696431696</v>
       </c>
-      <c r="K36" s="24" t="s">
+      <c r="K36" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="L36" s="24">
+      <c r="L36" s="22">
         <v>0.99988500000000002</v>
       </c>
-      <c r="M36" s="24">
+      <c r="M36" s="22">
         <v>0.999919</v>
       </c>
-      <c r="N36" s="21">
+      <c r="N36" s="10">
         <v>9.5714000000000006</v>
       </c>
-      <c r="O36" s="8">
+      <c r="O36" s="10">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="P36" s="8">
         <v>4.1655092592592591E-2</v>
       </c>
-      <c r="P36" s="4"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q36" s="4"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B37" s="1">
         <v>4</v>
       </c>
@@ -3181,24 +3285,27 @@
       <c r="J37" s="6">
         <v>0.99998579797621101</v>
       </c>
-      <c r="K37" s="24">
+      <c r="K37" s="22">
         <v>0.99997599999999998</v>
       </c>
-      <c r="L37" s="24">
+      <c r="L37" s="22">
         <v>0.99996799999999997</v>
       </c>
-      <c r="M37" s="24">
+      <c r="M37" s="22">
         <v>0.99997199999999997</v>
       </c>
-      <c r="N37" s="25">
+      <c r="N37" s="1">
         <v>8.5408000000000008</v>
       </c>
-      <c r="O37" s="8">
+      <c r="O37" s="1">
+        <v>6.0600000000000001E-2</v>
+      </c>
+      <c r="P37" s="8">
         <v>4.7118055555555559E-2</v>
       </c>
-      <c r="P37" s="4"/>
-    </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q37" s="4"/>
+    </row>
+    <row r="38" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B38" s="1">
         <v>4</v>
       </c>
@@ -3226,24 +3333,27 @@
       <c r="J38" s="6">
         <v>0.99997869696431696</v>
       </c>
-      <c r="K38" s="24">
+      <c r="K38" s="22">
         <v>0.99995400000000001</v>
       </c>
-      <c r="L38" s="24">
+      <c r="L38" s="22">
         <v>0.99988500000000002</v>
       </c>
-      <c r="M38" s="24">
+      <c r="M38" s="22">
         <v>0.999919</v>
       </c>
-      <c r="N38" s="21">
+      <c r="N38" s="10">
         <v>5.9768999999999997</v>
       </c>
-      <c r="O38" s="8">
+      <c r="O38" s="10">
+        <v>4.24E-2</v>
+      </c>
+      <c r="P38" s="8">
         <v>2.2881944444444444E-2</v>
       </c>
-      <c r="P38" s="4"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q38" s="4"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B39" s="1">
         <v>4</v>
       </c>
@@ -3271,24 +3381,27 @@
       <c r="J39" s="6">
         <v>0.99998579797621101</v>
       </c>
-      <c r="K39" s="24">
+      <c r="K39" s="22">
         <v>0.99997599999999998</v>
       </c>
-      <c r="L39" s="24">
+      <c r="L39" s="22">
         <v>0.99996799999999997</v>
       </c>
-      <c r="M39" s="24">
+      <c r="M39" s="22">
         <v>0.99997199999999997</v>
       </c>
-      <c r="N39" s="25">
+      <c r="N39" s="1">
         <v>6.0861999999999998</v>
       </c>
-      <c r="O39" s="8">
+      <c r="O39" s="1">
+        <v>4.3200000000000002E-2</v>
+      </c>
+      <c r="P39" s="8">
         <v>5.440972222222222E-2</v>
       </c>
-      <c r="P39" s="4"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q39" s="4"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B40" s="1">
         <v>4</v>
       </c>
@@ -3316,24 +3429,27 @@
       <c r="J40" s="6">
         <v>0.99998579797621101</v>
       </c>
-      <c r="K40" s="24">
+      <c r="K40" s="22">
         <v>0.99997599999999998</v>
       </c>
-      <c r="L40" s="24">
+      <c r="L40" s="22">
         <v>0.99996799999999997</v>
       </c>
-      <c r="M40" s="24">
+      <c r="M40" s="22">
         <v>0.99997199999999997</v>
       </c>
-      <c r="N40" s="21">
+      <c r="N40" s="10">
         <v>7.5895000000000001</v>
       </c>
-      <c r="O40" s="8">
+      <c r="O40" s="10">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="P40" s="8">
         <v>5.4467592592592595E-2</v>
       </c>
-      <c r="P40" s="4"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q40" s="4"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B41" s="1">
         <v>4</v>
       </c>
@@ -3361,24 +3477,27 @@
       <c r="J41" s="6">
         <v>0.99999289898810495</v>
       </c>
-      <c r="K41" s="24">
+      <c r="K41" s="22">
         <v>0.99999899999999997</v>
       </c>
-      <c r="L41" s="24">
+      <c r="L41" s="22">
         <v>0.99997000000000003</v>
       </c>
-      <c r="M41" s="24">
+      <c r="M41" s="22">
         <v>0.99998399999999998</v>
       </c>
-      <c r="N41" s="25">
+      <c r="N41" s="1">
         <v>5.7012999999999998</v>
       </c>
-      <c r="O41" s="8">
+      <c r="O41" s="1">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="P41" s="8">
         <v>0.16643518518518519</v>
       </c>
-      <c r="P41" s="4"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q41" s="4"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B42" s="1">
         <v>4</v>
       </c>
@@ -3406,24 +3525,27 @@
       <c r="J42" s="6">
         <v>0.99997869696431696</v>
       </c>
-      <c r="K42" s="24">
+      <c r="K42" s="22">
         <v>0.99997499999999995</v>
       </c>
-      <c r="L42" s="24">
+      <c r="L42" s="22">
         <v>0.99988500000000002</v>
       </c>
-      <c r="M42" s="24">
+      <c r="M42" s="22">
         <v>0.99992999999999999</v>
       </c>
-      <c r="N42" s="21">
+      <c r="N42" s="10">
         <v>5.7836999999999996</v>
       </c>
-      <c r="O42" s="8">
+      <c r="O42" s="10">
+        <v>4.1099999999999998E-2</v>
+      </c>
+      <c r="P42" s="8">
         <v>0.14592592592592593</v>
       </c>
-      <c r="P42" s="4"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q42" s="4"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B43" s="1">
         <v>4</v>
       </c>
@@ -3451,24 +3573,27 @@
       <c r="J43" s="6">
         <v>0.99999289898810495</v>
       </c>
-      <c r="K43" s="24">
+      <c r="K43" s="22">
         <v>0.99997800000000003</v>
       </c>
-      <c r="L43" s="24">
+      <c r="L43" s="22">
         <v>0.99999000000000005</v>
       </c>
-      <c r="M43" s="24">
+      <c r="M43" s="22">
         <v>0.99998799999999999</v>
       </c>
-      <c r="N43" s="25">
+      <c r="N43" s="1">
         <v>5.8055000000000003</v>
       </c>
-      <c r="O43" s="8">
+      <c r="O43" s="1">
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="P43" s="8">
         <v>2.9305555555555557E-2</v>
       </c>
-      <c r="P43" s="4"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="Q43" s="4"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -3480,7 +3605,7 @@
       <c r="J44" s="6"/>
       <c r="K44" s="4"/>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -3492,7 +3617,7 @@
       <c r="J45" s="6"/>
       <c r="K45" s="4"/>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -3504,7 +3629,7 @@
       <c r="J46" s="8"/>
       <c r="K46" s="4"/>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -3516,7 +3641,7 @@
       <c r="J47" s="8"/>
       <c r="K47" s="4"/>
     </row>
-    <row r="48" spans="2:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:17" ht="29" x14ac:dyDescent="0.35">
       <c r="B48" s="18" t="s">
         <v>83</v>
       </c>
@@ -3545,7 +3670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B49" s="10">
         <v>4</v>
       </c>
@@ -3572,7 +3697,7 @@
       </c>
       <c r="J49" s="4"/>
     </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B50" s="14">
         <v>4</v>
       </c>
@@ -3598,7 +3723,7 @@
         <v>9.2824074074074076E-3</v>
       </c>
     </row>
-    <row r="53" spans="2:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:16" ht="29" x14ac:dyDescent="0.35">
       <c r="B53" s="18" t="s">
         <v>83</v>
       </c>
@@ -3636,29 +3761,32 @@
         <v>124</v>
       </c>
       <c r="N53" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="O53" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="O53" s="20" t="s">
+      <c r="P53" s="20" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B54" s="21" t="s">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B54" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="C54" s="21" t="s">
+      <c r="C54" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="D54" s="21" t="s">
+      <c r="D54" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E54" s="22">
+      <c r="E54" s="11">
         <v>11398</v>
       </c>
-      <c r="F54" s="22">
+      <c r="F54" s="11">
         <v>11398</v>
       </c>
-      <c r="G54" s="22">
+      <c r="G54" s="11">
         <v>33</v>
       </c>
       <c r="H54" s="12">
@@ -3667,22 +3795,25 @@
       <c r="I54" s="12">
         <v>0.44620599999999999</v>
       </c>
-      <c r="J54" s="21" t="s">
+      <c r="J54" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="K54" s="21" t="s">
+      <c r="K54" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="L54" s="21" t="s">
+      <c r="L54" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="M54" s="21" t="s">
+      <c r="M54" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="N54" s="13">
+      <c r="N54" s="10">
+        <v>2.7E-2</v>
+      </c>
+      <c r="O54" s="13">
         <v>0.54584490740740743</v>
       </c>
-      <c r="O54" s="23"/>
+      <c r="P54" s="21"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
